--- a/BiblioParsing/BiblioParsing_RefFiles/Institutions_types.xlsx
+++ b/BiblioParsing/BiblioParsing_RefFiles/Institutions_types.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AC265100\PyVenv\BiblioParsing\BiblioParsing\BiblioParsing_RefFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AC265100\Documents\BiblioMeter_App\LETI\Bibliometry\BiblioMeter_Files-6.2.0\Traitement Institutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3173EDB8-13F1-44E8-85A3-FEA4612400F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38475" yWindow="-1545" windowWidth="31815" windowHeight="23325"/>
+    <workbookView xWindow="37860" yWindow="4950" windowWidth="35880" windowHeight="10380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Norm affiliation types" sheetId="1" r:id="rId1"/>
@@ -19,20 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="122">
   <si>
     <t>Agn</t>
   </si>
@@ -46,15 +42,9 @@
     <t>Inst</t>
   </si>
   <si>
-    <t>Institut</t>
-  </si>
-  <si>
     <t>Firm</t>
   </si>
   <si>
-    <t>Insductriel ; Startup</t>
-  </si>
-  <si>
     <t>Dept</t>
   </si>
   <si>
@@ -97,12 +87,6 @@
     <t>Company; Startup</t>
   </si>
   <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Département</t>
-  </si>
-  <si>
     <t>Université</t>
   </si>
   <si>
@@ -115,12 +99,6 @@
     <t>Centre de recherche</t>
   </si>
   <si>
-    <t>Platform</t>
-  </si>
-  <si>
-    <t>Plateforme</t>
-  </si>
-  <si>
     <t>Institute</t>
   </si>
   <si>
@@ -130,9 +108,6 @@
     <t xml:space="preserve">Laboratory </t>
   </si>
   <si>
-    <t>Laboratoire</t>
-  </si>
-  <si>
     <t>_</t>
   </si>
   <si>
@@ -244,9 +219,6 @@
     <t>School</t>
   </si>
   <si>
-    <t>Grande école</t>
-  </si>
-  <si>
     <t>Campus ; Incubateur ; Technopôle ; Bâtiment</t>
   </si>
   <si>
@@ -290,13 +262,181 @@
   </si>
   <si>
     <t>Laboratoire d'excellence</t>
+  </si>
+  <si>
+    <t>CNRS-Lab</t>
+  </si>
+  <si>
+    <t>CEA-Lab</t>
+  </si>
+  <si>
+    <t>Univ-Lab</t>
+  </si>
+  <si>
+    <t>Laboratoire universitaire hors CNRS</t>
+  </si>
+  <si>
+    <t>CEA-Serv</t>
+  </si>
+  <si>
+    <t>Laboratoire hors CEA, CNRS et propre université</t>
+  </si>
+  <si>
+    <t>Service hors CEA</t>
+  </si>
+  <si>
+    <t>Laboratoire UMR ou UPR CNRS</t>
+  </si>
+  <si>
+    <t>CEA-Dept</t>
+  </si>
+  <si>
+    <t>Département hors CEA</t>
+  </si>
+  <si>
+    <t>CEA-Inst</t>
+  </si>
+  <si>
+    <t>Institut CEA</t>
+  </si>
+  <si>
+    <t>Institut hors CEA</t>
+  </si>
+  <si>
+    <t>CEA-Div</t>
+  </si>
+  <si>
+    <t>Direction CEA</t>
+  </si>
+  <si>
+    <t>Direction hors CEA</t>
+  </si>
+  <si>
+    <t>Rto</t>
+  </si>
+  <si>
+    <t>LETI-Dept</t>
+  </si>
+  <si>
+    <t>Département CEA hors Leti</t>
+  </si>
+  <si>
+    <t>Département Leti</t>
+  </si>
+  <si>
+    <t>LETI-Serv</t>
+  </si>
+  <si>
+    <t>LETI-Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service CEA hors Leti, y compris UMR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratoire CEA hors LETI, y compris UMR </t>
+  </si>
+  <si>
+    <t>Service Leti</t>
+  </si>
+  <si>
+    <t>Laboratoire Leti</t>
+  </si>
+  <si>
+    <t>Irt</t>
+  </si>
+  <si>
+    <t>Institut de recherche technologique</t>
+  </si>
+  <si>
+    <t>Research and Technology Organization</t>
+  </si>
+  <si>
+    <t>Organisation de recherche et technologie</t>
+  </si>
+  <si>
+    <t>Plateforme autre que CNRS</t>
+  </si>
+  <si>
+    <t>Platform other than CNRS</t>
+  </si>
+  <si>
+    <t>CNRS-Pltf</t>
+  </si>
+  <si>
+    <t>Platform of CNRS</t>
+  </si>
+  <si>
+    <t>Plateforme CNRS</t>
+  </si>
+  <si>
+    <t>Industriel ; Startup</t>
+  </si>
+  <si>
+    <t>Art</t>
+  </si>
+  <si>
+    <t>Organismes artistiques</t>
+  </si>
+  <si>
+    <t>Art organismes</t>
+  </si>
+  <si>
+    <t>Dsch</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>É</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>coles docrorales</t>
+    </r>
+  </si>
+  <si>
+    <t>Gsch</t>
+  </si>
+  <si>
+    <t>Grandes Écoles</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>É</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>cole</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -311,6 +451,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -333,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -346,6 +492,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,455 +809,680 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.69921875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.09765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.8984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.0703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.92578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.69921875" style="1"/>
+    <col min="5" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>58</v>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
+      <c r="B3" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
+      <c r="B6" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>55</v>
+      <c r="B7" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>38</v>
+      <c r="B8" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>48</v>
+      <c r="B9" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
+      <c r="B10" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>75</v>
+      <c r="B11" s="5" t="s">
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
+      <c r="B13" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>64</v>
+      <c r="B14" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>81</v>
+      <c r="B15" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>83</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>71</v>
+      <c r="C36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="B10:D44">
-    <sortCondition ref="B1:B44"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B12:D47">
+    <sortCondition ref="B1:B47"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>